--- a/datasets/WBC.xlsx
+++ b/datasets/WBC.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\papachristou\GoogleDrive\Teaching\STAT511\Lectures\Datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rowanads.rowan.edu\home\tsui\Documents\GitHub\manctsui.github.io\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E7C1DA-F191-41B3-97F3-C02538D75F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9195"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -40,9 +41,6 @@
   </si>
   <si>
     <t>Jim</t>
-  </si>
-  <si>
-    <t>.</t>
   </si>
   <si>
     <t>Al</t>
@@ -114,7 +112,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -925,61 +923,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" style="2"/>
-    <col min="6" max="12" width="6.28515625" style="2" customWidth="1"/>
+    <col min="1" max="2" width="6.26953125" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" style="2"/>
+    <col min="6" max="12" width="6.26953125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1">
         <v>27674</v>
@@ -994,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2">
         <v>3</v>
@@ -1012,12 +1010,12 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1">
         <v>37094</v>
@@ -1032,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2">
         <v>6</v>
@@ -1040,9 +1038,7 @@
       <c r="I3" s="3">
         <v>14.8</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="3">
         <v>14.1</v>
       </c>
@@ -1050,12 +1046,12 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>27275</v>
@@ -1070,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2">
         <v>8</v>
@@ -1088,12 +1084,12 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <v>26486</v>
@@ -1108,10 +1104,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I5" s="3">
         <v>14.2</v>
@@ -1126,12 +1119,12 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
         <v>37480</v>
@@ -1146,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2">
         <v>2</v>
@@ -1164,12 +1157,12 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1">
         <v>29187</v>
@@ -1184,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H7" s="2">
         <v>3</v>
@@ -1202,12 +1195,12 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
         <v>21050</v>
@@ -1222,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="2">
         <v>7</v>
@@ -1240,12 +1233,12 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1">
         <v>22196</v>
@@ -1260,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2">
         <v>2</v>
@@ -1278,12 +1271,12 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1">
         <v>36697</v>
@@ -1298,7 +1291,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2">
         <v>6</v>
@@ -1316,12 +1309,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>36391</v>
@@ -1336,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
@@ -1354,12 +1347,12 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1">
         <v>34283</v>
@@ -1374,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -1392,12 +1385,12 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
         <v>22792</v>
@@ -1412,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="2">
         <v>6</v>
@@ -1423,9 +1416,7 @@
       <c r="J13" s="3">
         <v>12.5</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="K13" s="3"/>
       <c r="L13" s="3">
         <v>12.7</v>
       </c>
